--- a/artfynd/A 48075-2023 artfynd.xlsx
+++ b/artfynd/A 48075-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -789,6 +789,238 @@
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>121462186</v>
+      </c>
+      <c r="B3" t="n">
+        <v>91989</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Skrovlig taggsvamp</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hydnellum scabrosum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Gladaberg3, Vb</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>717022</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7147177</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>äldre</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Mariana Jussila Wahlberg</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Mariana Jussila Wahlberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>121466364</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91977</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Gladaberg7, Vb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>717237</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7147109</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-09-06</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>äldre</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Mariana Jussila Wahlberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Mariana Jussila Wahlberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 48075-2023 artfynd.xlsx
+++ b/artfynd/A 48075-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121435498</v>
       </c>
       <c r="B2" t="n">
-        <v>89380</v>
+        <v>89387</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>121462186</v>
       </c>
       <c r="B3" t="n">
-        <v>91989</v>
+        <v>92001</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 48075-2023 artfynd.xlsx
+++ b/artfynd/A 48075-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121435498</v>
       </c>
       <c r="B2" t="n">
-        <v>89387</v>
+        <v>89388</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121462186</v>
+        <v>121466364</v>
       </c>
       <c r="B3" t="n">
-        <v>92001</v>
+        <v>91978</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,21 +807,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -830,14 +830,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gladaberg3, Vb</t>
+          <t>Gladaberg7, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>717022</v>
+        <v>717237</v>
       </c>
       <c r="R3" t="n">
-        <v>7147177</v>
+        <v>7147109</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,12 +864,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121466364</v>
+        <v>121462186</v>
       </c>
       <c r="B4" t="n">
-        <v>91977</v>
+        <v>92002</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,21 +923,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -946,14 +946,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gladaberg7, Vb</t>
+          <t>Gladaberg3, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>717237</v>
+        <v>717022</v>
       </c>
       <c r="R4" t="n">
-        <v>7147109</v>
+        <v>7147177</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,12 +980,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 48075-2023 artfynd.xlsx
+++ b/artfynd/A 48075-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121435498</v>
       </c>
       <c r="B2" t="n">
-        <v>89388</v>
+        <v>89391</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121466364</v>
+        <v>121462186</v>
       </c>
       <c r="B3" t="n">
-        <v>91978</v>
+        <v>92005</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,21 +807,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -830,14 +830,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gladaberg7, Vb</t>
+          <t>Gladaberg3, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>717237</v>
+        <v>717022</v>
       </c>
       <c r="R3" t="n">
-        <v>7147109</v>
+        <v>7147177</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,12 +864,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121462186</v>
+        <v>121466364</v>
       </c>
       <c r="B4" t="n">
-        <v>92002</v>
+        <v>91981</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,21 +923,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -946,14 +946,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gladaberg3, Vb</t>
+          <t>Gladaberg7, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>717022</v>
+        <v>717237</v>
       </c>
       <c r="R4" t="n">
-        <v>7147177</v>
+        <v>7147109</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,12 +980,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 48075-2023 artfynd.xlsx
+++ b/artfynd/A 48075-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121435498</v>
       </c>
       <c r="B2" t="n">
-        <v>89391</v>
+        <v>89395</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>121462186</v>
       </c>
       <c r="B3" t="n">
-        <v>92005</v>
+        <v>92011</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>121466364</v>
       </c>
       <c r="B4" t="n">
-        <v>91981</v>
+        <v>91987</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 48075-2023 artfynd.xlsx
+++ b/artfynd/A 48075-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121435498</v>
       </c>
       <c r="B2" t="n">
-        <v>89395</v>
+        <v>89396</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121462186</v>
+        <v>121466364</v>
       </c>
       <c r="B3" t="n">
-        <v>92011</v>
+        <v>91988</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,21 +807,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -830,14 +830,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gladaberg3, Vb</t>
+          <t>Gladaberg7, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>717022</v>
+        <v>717237</v>
       </c>
       <c r="R3" t="n">
-        <v>7147177</v>
+        <v>7147109</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,12 +864,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121466364</v>
+        <v>121462186</v>
       </c>
       <c r="B4" t="n">
-        <v>91987</v>
+        <v>92012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,21 +923,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -946,14 +946,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gladaberg7, Vb</t>
+          <t>Gladaberg3, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>717237</v>
+        <v>717022</v>
       </c>
       <c r="R4" t="n">
-        <v>7147109</v>
+        <v>7147177</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,12 +980,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 48075-2023 artfynd.xlsx
+++ b/artfynd/A 48075-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121466364</v>
+        <v>121462186</v>
       </c>
       <c r="B3" t="n">
-        <v>91988</v>
+        <v>92012</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,21 +807,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -830,14 +830,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gladaberg7, Vb</t>
+          <t>Gladaberg3, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>717237</v>
+        <v>717022</v>
       </c>
       <c r="R3" t="n">
-        <v>7147109</v>
+        <v>7147177</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,12 +864,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-09-06</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121462186</v>
+        <v>121466364</v>
       </c>
       <c r="B4" t="n">
-        <v>92012</v>
+        <v>91988</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,21 +923,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -946,14 +946,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gladaberg3, Vb</t>
+          <t>Gladaberg7, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>717022</v>
+        <v>717237</v>
       </c>
       <c r="R4" t="n">
-        <v>7147177</v>
+        <v>7147109</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,12 +980,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-09-06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,6 +1020,118 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121631828</v>
+      </c>
+      <c r="B5" t="n">
+        <v>89396</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6276</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Goliatmusseron</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tricholoma matsutake</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>gladaberg7, Vb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>717167</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7147043</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>äldre</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mariana Jussila Wahlberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Mariana Jussila Wahlberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 48075-2023 artfynd.xlsx
+++ b/artfynd/A 48075-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121435498</v>
       </c>
       <c r="B2" t="n">
-        <v>89396</v>
+        <v>89403</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>121462186</v>
       </c>
       <c r="B3" t="n">
-        <v>92012</v>
+        <v>92020</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
         <v>121466364</v>
       </c>
       <c r="B4" t="n">
-        <v>91988</v>
+        <v>91996</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1026,7 +1026,7 @@
         <v>121631828</v>
       </c>
       <c r="B5" t="n">
-        <v>89396</v>
+        <v>89403</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 48075-2023 artfynd.xlsx
+++ b/artfynd/A 48075-2023 artfynd.xlsx
@@ -1135,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121756535</v>
+        <v>121756530</v>
       </c>
       <c r="B6" t="n">
-        <v>91998</v>
+        <v>89776</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1151,21 +1151,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4362</v>
+        <v>1962</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1174,14 +1174,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>gladaberg8, Vb</t>
+          <t>gladaberg11, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>717196</v>
+        <v>717228</v>
       </c>
       <c r="R6" t="n">
-        <v>7147157</v>
+        <v>7147131</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,12 +1208,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-10-02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-10-02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1231,9 +1231,24 @@
           <t>Sandtallskog</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>äldre</t>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # stump, silver # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1367,10 +1382,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121756530</v>
+        <v>121756535</v>
       </c>
       <c r="B8" t="n">
-        <v>89776</v>
+        <v>91998</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,21 +1398,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1962</v>
+        <v>4362</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1406,14 +1421,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>gladaberg11, Vb</t>
+          <t>gladaberg8, Vb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>717228</v>
+        <v>717196</v>
       </c>
       <c r="R8" t="n">
-        <v>7147131</v>
+        <v>7147157</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1440,12 +1455,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1463,24 +1478,9 @@
           <t>Sandtallskog</t>
         </is>
       </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # stump, silver # Pinus sylvestris</t>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>äldre</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>

--- a/artfynd/A 48075-2023 artfynd.xlsx
+++ b/artfynd/A 48075-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1135,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121756530</v>
+        <v>121756528</v>
       </c>
       <c r="B6" t="n">
-        <v>89776</v>
+        <v>91998</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1151,21 +1151,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1962</v>
+        <v>4362</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1174,14 +1174,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>gladaberg11, Vb</t>
+          <t>Gladaberg12, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>717228</v>
+        <v>717311</v>
       </c>
       <c r="R6" t="n">
-        <v>7147131</v>
+        <v>7147055</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,12 +1208,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1231,24 +1231,9 @@
           <t>Sandtallskog</t>
         </is>
       </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # stump, silver # Pinus sylvestris</t>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>äldre</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1266,10 +1251,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121756528</v>
+        <v>121756530</v>
       </c>
       <c r="B7" t="n">
-        <v>91998</v>
+        <v>89776</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1282,21 +1267,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4362</v>
+        <v>1962</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1305,14 +1290,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gladaberg12, Vb</t>
+          <t>gladaberg11, Vb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>717311</v>
+        <v>717228</v>
       </c>
       <c r="R7" t="n">
-        <v>7147055</v>
+        <v>7147131</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1339,12 +1324,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-10-02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2024-10-02</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,9 +1347,24 @@
           <t>Sandtallskog</t>
         </is>
       </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>äldre</t>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # stump, silver # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1496,6 +1496,122 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>121854261</v>
+      </c>
+      <c r="B9" t="n">
+        <v>92020</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Skrovlig taggsvamp</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hydnellum scabrosum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>gladaberg18, Vb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>717005</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7147166</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Vindeln</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Sandtallskog</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>äldre</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Mariana Jussila Wahlberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Mariana Jussila Wahlberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 48075-2023 artfynd.xlsx
+++ b/artfynd/A 48075-2023 artfynd.xlsx
@@ -1614,10 +1614,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121972536</v>
+        <v>121972017</v>
       </c>
       <c r="B10" t="n">
-        <v>92049</v>
+        <v>92047</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1630,21 +1630,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1653,14 +1653,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>gladaberg24, Vb</t>
+          <t>gladaberg21, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>717199</v>
+        <v>717146</v>
       </c>
       <c r="R10" t="n">
-        <v>7147036</v>
+        <v>7147163</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1730,10 +1730,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121972017</v>
+        <v>121972533</v>
       </c>
       <c r="B11" t="n">
-        <v>92047</v>
+        <v>89454</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1742,25 +1742,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4361</v>
+        <v>6276</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1769,14 +1769,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>gladaberg21, Vb</t>
+          <t>gladaberg26, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>717146</v>
+        <v>717013</v>
       </c>
       <c r="R11" t="n">
-        <v>7147163</v>
+        <v>7147156</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1846,10 +1846,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121972533</v>
+        <v>121972536</v>
       </c>
       <c r="B12" t="n">
-        <v>89454</v>
+        <v>92049</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1858,25 +1858,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6276</v>
+        <v>4362</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1885,14 +1885,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>gladaberg26, Vb</t>
+          <t>gladaberg24, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>717013</v>
+        <v>717199</v>
       </c>
       <c r="R12" t="n">
-        <v>7147156</v>
+        <v>7147036</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2310,10 +2310,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122032383</v>
+        <v>122032385</v>
       </c>
       <c r="B16" t="n">
-        <v>92071</v>
+        <v>89454</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2322,25 +2322,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2059</v>
+        <v>6276</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2349,14 +2349,14 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>gladaberg44, Vb</t>
+          <t>gladaberg43, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>717040</v>
+        <v>717203</v>
       </c>
       <c r="R16" t="n">
-        <v>7147142</v>
+        <v>7147231</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2426,10 +2426,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122032387</v>
+        <v>122032383</v>
       </c>
       <c r="B17" t="n">
-        <v>89454</v>
+        <v>92071</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2438,25 +2438,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6276</v>
+        <v>2059</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2465,14 +2465,14 @@
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>gladaberg42, Vb</t>
+          <t>gladaberg44, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>717138</v>
+        <v>717040</v>
       </c>
       <c r="R17" t="n">
-        <v>7147029</v>
+        <v>7147142</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2542,7 +2542,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122032385</v>
+        <v>122032387</v>
       </c>
       <c r="B18" t="n">
         <v>89454</v>
@@ -2581,14 +2581,14 @@
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>gladaberg43, Vb</t>
+          <t>gladaberg42, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>717203</v>
+        <v>717138</v>
       </c>
       <c r="R18" t="n">
-        <v>7147231</v>
+        <v>7147029</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2774,7 +2774,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122085239</v>
+        <v>122091612</v>
       </c>
       <c r="B20" t="n">
         <v>92047</v>
@@ -2813,14 +2813,14 @@
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>gladaberg50, Vb</t>
+          <t>gladaberg53, Vb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>717309</v>
+        <v>717176</v>
       </c>
       <c r="R20" t="n">
-        <v>7146939</v>
+        <v>7147221</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2890,10 +2890,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122091602</v>
+        <v>122085251</v>
       </c>
       <c r="B21" t="n">
-        <v>92071</v>
+        <v>89454</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2902,38 +2902,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2059</v>
+        <v>6276</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>gladaberg57, Vb</t>
+          <t>gladaberg48, Vb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>717274</v>
+        <v>717011</v>
       </c>
       <c r="R21" t="n">
-        <v>7147076</v>
+        <v>7147163</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3002,10 +3002,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122085242</v>
+        <v>122091604</v>
       </c>
       <c r="B22" t="n">
-        <v>89454</v>
+        <v>92071</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3014,25 +3014,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6276</v>
+        <v>2059</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3041,14 +3041,14 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>gladaberg49, Vb</t>
+          <t>gladaberg56, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>717095</v>
+        <v>717151</v>
       </c>
       <c r="R22" t="n">
-        <v>7147068</v>
+        <v>7147276</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3118,7 +3118,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122085251</v>
+        <v>122085242</v>
       </c>
       <c r="B23" t="n">
         <v>89454</v>
@@ -3152,16 +3152,19 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>gladaberg48, Vb</t>
+          <t>gladaberg49, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>717011</v>
+        <v>717095</v>
       </c>
       <c r="R23" t="n">
-        <v>7147163</v>
+        <v>7147068</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3202,6 +3205,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3230,7 +3234,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122091604</v>
+        <v>122091602</v>
       </c>
       <c r="B24" t="n">
         <v>92071</v>
@@ -3264,19 +3268,16 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>gladaberg56, Vb</t>
+          <t>gladaberg57, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>717151</v>
+        <v>717274</v>
       </c>
       <c r="R24" t="n">
-        <v>7147276</v>
+        <v>7147076</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3317,7 +3318,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3346,7 +3346,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122091612</v>
+        <v>122085239</v>
       </c>
       <c r="B25" t="n">
         <v>92047</v>
@@ -3385,14 +3385,14 @@
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>gladaberg53, Vb</t>
+          <t>gladaberg50, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>717176</v>
+        <v>717309</v>
       </c>
       <c r="R25" t="n">
-        <v>7147221</v>
+        <v>7146939</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3462,10 +3462,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122106356</v>
+        <v>122106363</v>
       </c>
       <c r="B26" t="n">
-        <v>89454</v>
+        <v>92071</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3474,25 +3474,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6276</v>
+        <v>2059</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3501,14 +3501,14 @@
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>gladaberg62, Vb</t>
+          <t>gladaberg60, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>717129</v>
+        <v>717060</v>
       </c>
       <c r="R26" t="n">
-        <v>7147026</v>
+        <v>7147112</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3578,10 +3578,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122106363</v>
+        <v>122106357</v>
       </c>
       <c r="B27" t="n">
-        <v>92071</v>
+        <v>92047</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3594,21 +3594,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3617,14 +3617,14 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>gladaberg60, Vb</t>
+          <t>gladaberg61, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>717060</v>
+        <v>717038</v>
       </c>
       <c r="R27" t="n">
-        <v>7147112</v>
+        <v>7147114</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3694,10 +3694,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122106357</v>
+        <v>122106356</v>
       </c>
       <c r="B28" t="n">
-        <v>92047</v>
+        <v>89454</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3706,25 +3706,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4361</v>
+        <v>6276</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3733,14 +3733,14 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>gladaberg61, Vb</t>
+          <t>gladaberg62, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>717038</v>
+        <v>717129</v>
       </c>
       <c r="R28" t="n">
-        <v>7147114</v>
+        <v>7147026</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3810,10 +3810,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122232491</v>
+        <v>122232479</v>
       </c>
       <c r="B29" t="n">
-        <v>92049</v>
+        <v>89454</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3822,25 +3822,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4362</v>
+        <v>6276</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3849,14 +3849,14 @@
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>gladaberg67, Vb</t>
+          <t>gladaberg70, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>717247</v>
+        <v>717126</v>
       </c>
       <c r="R29" t="n">
-        <v>7147095</v>
+        <v>7147085</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4042,10 +4042,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122232479</v>
+        <v>122232491</v>
       </c>
       <c r="B31" t="n">
-        <v>89454</v>
+        <v>92049</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4054,25 +4054,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6276</v>
+        <v>4362</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4081,14 +4081,14 @@
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>gladaberg70, Vb</t>
+          <t>gladaberg67, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>717126</v>
+        <v>717247</v>
       </c>
       <c r="R31" t="n">
-        <v>7147085</v>
+        <v>7147095</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4158,10 +4158,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122347980</v>
+        <v>122347983</v>
       </c>
       <c r="B32" t="n">
-        <v>89454</v>
+        <v>92083</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4170,25 +4170,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6276</v>
+        <v>5449</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4197,14 +4197,14 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>gladaberg72, Vb</t>
+          <t>gladaberg71, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>717040</v>
+        <v>717248</v>
       </c>
       <c r="R32" t="n">
-        <v>7147136</v>
+        <v>7147108</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4274,10 +4274,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122347973</v>
+        <v>122347978</v>
       </c>
       <c r="B33" t="n">
-        <v>78382</v>
+        <v>89454</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4286,41 +4286,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>6276</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>gladaberg74, Vb</t>
+          <t>gladaberg73, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>717095</v>
+        <v>717180</v>
       </c>
       <c r="R33" t="n">
-        <v>7147049</v>
+        <v>7147242</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4361,7 +4358,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4370,24 +4366,9 @@
           <t>Sandtallskog</t>
         </is>
       </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Stump # låg,sotad # Pinus sylvestris</t>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>äldre</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4405,10 +4386,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122347978</v>
+        <v>122347973</v>
       </c>
       <c r="B34" t="n">
-        <v>89454</v>
+        <v>78382</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4417,38 +4398,41 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6276</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>gladaberg73, Vb</t>
+          <t>gladaberg74, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>717180</v>
+        <v>717095</v>
       </c>
       <c r="R34" t="n">
-        <v>7147242</v>
+        <v>7147049</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4489,6 +4473,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4497,9 +4482,24 @@
           <t>Sandtallskog</t>
         </is>
       </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>äldre</t>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Stump # låg,sotad # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4517,10 +4517,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122347983</v>
+        <v>122347980</v>
       </c>
       <c r="B35" t="n">
-        <v>92083</v>
+        <v>89454</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4529,25 +4529,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5449</v>
+        <v>6276</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4556,14 +4556,14 @@
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>gladaberg71, Vb</t>
+          <t>gladaberg72, Vb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>717248</v>
+        <v>717040</v>
       </c>
       <c r="R35" t="n">
-        <v>7147108</v>
+        <v>7147136</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>

--- a/artfynd/A 48075-2023 artfynd.xlsx
+++ b/artfynd/A 48075-2023 artfynd.xlsx
@@ -1617,7 +1617,7 @@
         <v>121972017</v>
       </c>
       <c r="B10" t="n">
-        <v>92047</v>
+        <v>92057</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1730,10 +1730,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121972533</v>
+        <v>121972536</v>
       </c>
       <c r="B11" t="n">
-        <v>89454</v>
+        <v>92059</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1742,25 +1742,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6276</v>
+        <v>4362</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1769,14 +1769,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>gladaberg26, Vb</t>
+          <t>gladaberg24, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>717013</v>
+        <v>717199</v>
       </c>
       <c r="R11" t="n">
-        <v>7147156</v>
+        <v>7147036</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1846,10 +1846,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121972536</v>
+        <v>121972533</v>
       </c>
       <c r="B12" t="n">
-        <v>92049</v>
+        <v>89464</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1858,25 +1858,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4362</v>
+        <v>6276</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1885,14 +1885,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>gladaberg24, Vb</t>
+          <t>gladaberg26, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>717199</v>
+        <v>717013</v>
       </c>
       <c r="R12" t="n">
-        <v>7147036</v>
+        <v>7147156</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1965,7 +1965,7 @@
         <v>121972026</v>
       </c>
       <c r="B13" t="n">
-        <v>92071</v>
+        <v>92081</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2078,10 +2078,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122009529</v>
+        <v>122009541</v>
       </c>
       <c r="B14" t="n">
-        <v>92049</v>
+        <v>89464</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2090,25 +2090,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4362</v>
+        <v>6276</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2117,14 +2117,14 @@
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>gladaberg41, Vb</t>
+          <t>gladaberg38, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>717086</v>
+        <v>717187</v>
       </c>
       <c r="R14" t="n">
-        <v>7147042</v>
+        <v>7147212</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2194,10 +2194,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122009541</v>
+        <v>122009529</v>
       </c>
       <c r="B15" t="n">
-        <v>89454</v>
+        <v>92059</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2206,25 +2206,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6276</v>
+        <v>4362</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2233,14 +2233,14 @@
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>gladaberg38, Vb</t>
+          <t>gladaberg41, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>717187</v>
+        <v>717086</v>
       </c>
       <c r="R15" t="n">
-        <v>7147212</v>
+        <v>7147042</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2313,7 +2313,7 @@
         <v>122032385</v>
       </c>
       <c r="B16" t="n">
-        <v>89454</v>
+        <v>89464</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>122032383</v>
       </c>
       <c r="B17" t="n">
-        <v>92071</v>
+        <v>92081</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>122032387</v>
       </c>
       <c r="B18" t="n">
-        <v>89454</v>
+        <v>89464</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2658,10 +2658,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122091614</v>
+        <v>122091604</v>
       </c>
       <c r="B19" t="n">
-        <v>92071</v>
+        <v>92081</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2697,14 +2697,14 @@
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>gladaberg52, Vb</t>
+          <t>gladaberg56, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>717310</v>
+        <v>717151</v>
       </c>
       <c r="R19" t="n">
-        <v>7147007</v>
+        <v>7147276</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2777,7 +2777,7 @@
         <v>122091612</v>
       </c>
       <c r="B20" t="n">
-        <v>92047</v>
+        <v>92057</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2890,10 +2890,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122085251</v>
+        <v>122091614</v>
       </c>
       <c r="B21" t="n">
-        <v>89454</v>
+        <v>92081</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2902,38 +2902,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6276</v>
+        <v>2059</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>gladaberg48, Vb</t>
+          <t>gladaberg52, Vb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>717011</v>
+        <v>717310</v>
       </c>
       <c r="R21" t="n">
-        <v>7147163</v>
+        <v>7147007</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2974,6 +2977,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3002,10 +3006,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122091604</v>
+        <v>122091602</v>
       </c>
       <c r="B22" t="n">
-        <v>92071</v>
+        <v>92081</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3036,19 +3040,16 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>gladaberg56, Vb</t>
+          <t>gladaberg57, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>717151</v>
+        <v>717274</v>
       </c>
       <c r="R22" t="n">
-        <v>7147276</v>
+        <v>7147076</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3089,7 +3090,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3118,10 +3118,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122085242</v>
+        <v>122085251</v>
       </c>
       <c r="B23" t="n">
-        <v>89454</v>
+        <v>89464</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3152,19 +3152,16 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>gladaberg49, Vb</t>
+          <t>gladaberg48, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>717095</v>
+        <v>717011</v>
       </c>
       <c r="R23" t="n">
-        <v>7147068</v>
+        <v>7147163</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3205,7 +3202,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3234,10 +3230,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122091602</v>
+        <v>122085239</v>
       </c>
       <c r="B24" t="n">
-        <v>92071</v>
+        <v>92057</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3250,34 +3246,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>gladaberg57, Vb</t>
+          <t>gladaberg50, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>717274</v>
+        <v>717309</v>
       </c>
       <c r="R24" t="n">
-        <v>7147076</v>
+        <v>7146939</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3318,6 +3317,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3346,10 +3346,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122085239</v>
+        <v>122085242</v>
       </c>
       <c r="B25" t="n">
-        <v>92047</v>
+        <v>89464</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3358,25 +3358,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4361</v>
+        <v>6276</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3385,14 +3385,14 @@
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>gladaberg50, Vb</t>
+          <t>gladaberg49, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>717309</v>
+        <v>717095</v>
       </c>
       <c r="R25" t="n">
-        <v>7146939</v>
+        <v>7147068</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3462,10 +3462,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122106363</v>
+        <v>122106357</v>
       </c>
       <c r="B26" t="n">
-        <v>92071</v>
+        <v>92057</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3478,21 +3478,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3501,14 +3501,14 @@
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>gladaberg60, Vb</t>
+          <t>gladaberg61, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>717060</v>
+        <v>717038</v>
       </c>
       <c r="R26" t="n">
-        <v>7147112</v>
+        <v>7147114</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3578,10 +3578,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122106357</v>
+        <v>122106363</v>
       </c>
       <c r="B27" t="n">
-        <v>92047</v>
+        <v>92081</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3594,21 +3594,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3617,14 +3617,14 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>gladaberg61, Vb</t>
+          <t>gladaberg60, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>717038</v>
+        <v>717060</v>
       </c>
       <c r="R27" t="n">
-        <v>7147114</v>
+        <v>7147112</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3697,7 +3697,7 @@
         <v>122106356</v>
       </c>
       <c r="B28" t="n">
-        <v>89454</v>
+        <v>89464</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3810,10 +3810,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122232479</v>
+        <v>122232491</v>
       </c>
       <c r="B29" t="n">
-        <v>89454</v>
+        <v>92059</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3822,25 +3822,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6276</v>
+        <v>4362</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3849,14 +3849,14 @@
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>gladaberg70, Vb</t>
+          <t>gladaberg67, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>717126</v>
+        <v>717247</v>
       </c>
       <c r="R29" t="n">
-        <v>7147085</v>
+        <v>7147095</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3926,10 +3926,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122232499</v>
+        <v>122232479</v>
       </c>
       <c r="B30" t="n">
-        <v>92071</v>
+        <v>89464</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3938,25 +3938,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2059</v>
+        <v>6276</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3965,14 +3965,14 @@
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>gladaberg64, Vb</t>
+          <t>gladaberg70, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>717129</v>
+        <v>717126</v>
       </c>
       <c r="R30" t="n">
-        <v>7147180</v>
+        <v>7147085</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4042,10 +4042,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122232491</v>
+        <v>122232499</v>
       </c>
       <c r="B31" t="n">
-        <v>92049</v>
+        <v>92081</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4058,21 +4058,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4081,14 +4081,14 @@
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>gladaberg67, Vb</t>
+          <t>gladaberg64, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>717247</v>
+        <v>717129</v>
       </c>
       <c r="R31" t="n">
-        <v>7147095</v>
+        <v>7147180</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4158,10 +4158,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122347983</v>
+        <v>122347973</v>
       </c>
       <c r="B32" t="n">
-        <v>92083</v>
+        <v>78383</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4174,21 +4174,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5449</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4197,14 +4197,14 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>gladaberg71, Vb</t>
+          <t>gladaberg74, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>717248</v>
+        <v>717095</v>
       </c>
       <c r="R32" t="n">
-        <v>7147108</v>
+        <v>7147049</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4254,9 +4254,24 @@
           <t>Sandtallskog</t>
         </is>
       </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>äldre</t>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Stump # låg,sotad # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4277,7 +4292,7 @@
         <v>122347978</v>
       </c>
       <c r="B33" t="n">
-        <v>89454</v>
+        <v>89464</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4386,10 +4401,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122347973</v>
+        <v>122347983</v>
       </c>
       <c r="B34" t="n">
-        <v>78382</v>
+        <v>92093</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4402,21 +4417,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>5449</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4425,14 +4440,14 @@
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>gladaberg74, Vb</t>
+          <t>gladaberg71, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>717095</v>
+        <v>717248</v>
       </c>
       <c r="R34" t="n">
-        <v>7147049</v>
+        <v>7147108</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4482,24 +4497,9 @@
           <t>Sandtallskog</t>
         </is>
       </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Stump # låg,sotad # Pinus sylvestris</t>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>äldre</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4520,7 +4520,7 @@
         <v>122347980</v>
       </c>
       <c r="B35" t="n">
-        <v>89454</v>
+        <v>89464</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>

--- a/artfynd/A 48075-2023 artfynd.xlsx
+++ b/artfynd/A 48075-2023 artfynd.xlsx
@@ -1614,10 +1614,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121972017</v>
+        <v>121972026</v>
       </c>
       <c r="B10" t="n">
-        <v>92057</v>
+        <v>92081</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1630,21 +1630,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1653,14 +1653,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>gladaberg21, Vb</t>
+          <t>gladaberg20, Vb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>717146</v>
+        <v>717086</v>
       </c>
       <c r="R10" t="n">
-        <v>7147163</v>
+        <v>7147084</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1846,10 +1846,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121972533</v>
+        <v>121972017</v>
       </c>
       <c r="B12" t="n">
-        <v>89464</v>
+        <v>92057</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1858,25 +1858,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6276</v>
+        <v>4361</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1885,14 +1885,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>gladaberg26, Vb</t>
+          <t>gladaberg21, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>717013</v>
+        <v>717146</v>
       </c>
       <c r="R12" t="n">
-        <v>7147156</v>
+        <v>7147163</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1962,10 +1962,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121972026</v>
+        <v>121972533</v>
       </c>
       <c r="B13" t="n">
-        <v>92081</v>
+        <v>89464</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1974,25 +1974,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2059</v>
+        <v>6276</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2001,14 +2001,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>gladaberg20, Vb</t>
+          <t>gladaberg26, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>717086</v>
+        <v>717013</v>
       </c>
       <c r="R13" t="n">
-        <v>7147084</v>
+        <v>7147156</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2078,10 +2078,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122009541</v>
+        <v>122009529</v>
       </c>
       <c r="B14" t="n">
-        <v>89464</v>
+        <v>92059</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2090,25 +2090,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6276</v>
+        <v>4362</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2117,14 +2117,14 @@
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>gladaberg38, Vb</t>
+          <t>gladaberg41, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>717187</v>
+        <v>717086</v>
       </c>
       <c r="R14" t="n">
-        <v>7147212</v>
+        <v>7147042</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2194,10 +2194,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122009529</v>
+        <v>122009541</v>
       </c>
       <c r="B15" t="n">
-        <v>92059</v>
+        <v>89464</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2206,25 +2206,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4362</v>
+        <v>6276</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2233,14 +2233,14 @@
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>gladaberg41, Vb</t>
+          <t>gladaberg38, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>717086</v>
+        <v>717187</v>
       </c>
       <c r="R15" t="n">
-        <v>7147042</v>
+        <v>7147212</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2310,7 +2310,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122032385</v>
+        <v>122032387</v>
       </c>
       <c r="B16" t="n">
         <v>89464</v>
@@ -2349,14 +2349,14 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>gladaberg43, Vb</t>
+          <t>gladaberg42, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>717203</v>
+        <v>717138</v>
       </c>
       <c r="R16" t="n">
-        <v>7147231</v>
+        <v>7147029</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2426,10 +2426,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122032383</v>
+        <v>122032385</v>
       </c>
       <c r="B17" t="n">
-        <v>92081</v>
+        <v>89464</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2438,25 +2438,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2059</v>
+        <v>6276</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2465,14 +2465,14 @@
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>gladaberg44, Vb</t>
+          <t>gladaberg43, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>717040</v>
+        <v>717203</v>
       </c>
       <c r="R17" t="n">
-        <v>7147142</v>
+        <v>7147231</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2542,10 +2542,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122032387</v>
+        <v>122032383</v>
       </c>
       <c r="B18" t="n">
-        <v>89464</v>
+        <v>92081</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2554,25 +2554,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6276</v>
+        <v>2059</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2581,14 +2581,14 @@
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>gladaberg42, Vb</t>
+          <t>gladaberg44, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>717138</v>
+        <v>717040</v>
       </c>
       <c r="R18" t="n">
-        <v>7147029</v>
+        <v>7147142</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2658,10 +2658,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122091604</v>
+        <v>122085251</v>
       </c>
       <c r="B19" t="n">
-        <v>92081</v>
+        <v>89464</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2670,41 +2670,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2059</v>
+        <v>6276</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>gladaberg56, Vb</t>
+          <t>gladaberg48, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>717151</v>
+        <v>717011</v>
       </c>
       <c r="R19" t="n">
-        <v>7147276</v>
+        <v>7147163</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2745,7 +2742,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2890,7 +2886,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122091614</v>
+        <v>122091604</v>
       </c>
       <c r="B21" t="n">
         <v>92081</v>
@@ -2929,14 +2925,14 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>gladaberg52, Vb</t>
+          <t>gladaberg56, Vb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>717310</v>
+        <v>717151</v>
       </c>
       <c r="R21" t="n">
-        <v>7147007</v>
+        <v>7147276</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3118,10 +3114,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122085251</v>
+        <v>122091614</v>
       </c>
       <c r="B23" t="n">
-        <v>89464</v>
+        <v>92081</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3130,38 +3126,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6276</v>
+        <v>2059</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>gladaberg48, Vb</t>
+          <t>gladaberg52, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>717011</v>
+        <v>717310</v>
       </c>
       <c r="R23" t="n">
-        <v>7147163</v>
+        <v>7147007</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3202,6 +3201,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3230,10 +3230,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122085239</v>
+        <v>122085242</v>
       </c>
       <c r="B24" t="n">
-        <v>92057</v>
+        <v>89464</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3242,25 +3242,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4361</v>
+        <v>6276</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3269,14 +3269,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>gladaberg50, Vb</t>
+          <t>gladaberg49, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>717309</v>
+        <v>717095</v>
       </c>
       <c r="R24" t="n">
-        <v>7146939</v>
+        <v>7147068</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3346,10 +3346,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122085242</v>
+        <v>122085239</v>
       </c>
       <c r="B25" t="n">
-        <v>89464</v>
+        <v>92057</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3358,25 +3358,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6276</v>
+        <v>4361</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3385,14 +3385,14 @@
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>gladaberg49, Vb</t>
+          <t>gladaberg50, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>717095</v>
+        <v>717309</v>
       </c>
       <c r="R25" t="n">
-        <v>7147068</v>
+        <v>7146939</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3578,10 +3578,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122106363</v>
+        <v>122106356</v>
       </c>
       <c r="B27" t="n">
-        <v>92081</v>
+        <v>89464</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3590,25 +3590,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2059</v>
+        <v>6276</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3617,14 +3617,14 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>gladaberg60, Vb</t>
+          <t>gladaberg62, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>717060</v>
+        <v>717129</v>
       </c>
       <c r="R27" t="n">
-        <v>7147112</v>
+        <v>7147026</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3694,10 +3694,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122106356</v>
+        <v>122106363</v>
       </c>
       <c r="B28" t="n">
-        <v>89464</v>
+        <v>92081</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3706,25 +3706,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6276</v>
+        <v>2059</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3733,14 +3733,14 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>gladaberg62, Vb</t>
+          <t>gladaberg60, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>717129</v>
+        <v>717060</v>
       </c>
       <c r="R28" t="n">
-        <v>7147026</v>
+        <v>7147112</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3810,10 +3810,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122232491</v>
+        <v>122232479</v>
       </c>
       <c r="B29" t="n">
-        <v>92059</v>
+        <v>89464</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3822,25 +3822,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4362</v>
+        <v>6276</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3849,14 +3849,14 @@
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>gladaberg67, Vb</t>
+          <t>gladaberg70, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>717247</v>
+        <v>717126</v>
       </c>
       <c r="R29" t="n">
-        <v>7147095</v>
+        <v>7147085</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3926,10 +3926,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122232479</v>
+        <v>122232491</v>
       </c>
       <c r="B30" t="n">
-        <v>89464</v>
+        <v>92059</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3938,25 +3938,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6276</v>
+        <v>4362</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3965,14 +3965,14 @@
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>gladaberg70, Vb</t>
+          <t>gladaberg67, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>717126</v>
+        <v>717247</v>
       </c>
       <c r="R30" t="n">
-        <v>7147085</v>
+        <v>7147095</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4158,10 +4158,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122347973</v>
+        <v>122347980</v>
       </c>
       <c r="B32" t="n">
-        <v>78383</v>
+        <v>89464</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4170,25 +4170,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>6276</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4197,14 +4197,14 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>gladaberg74, Vb</t>
+          <t>gladaberg72, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>717095</v>
+        <v>717040</v>
       </c>
       <c r="R32" t="n">
-        <v>7147049</v>
+        <v>7147136</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4254,24 +4254,9 @@
           <t>Sandtallskog</t>
         </is>
       </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Stump # låg,sotad # Pinus sylvestris</t>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>äldre</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4289,10 +4274,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122347978</v>
+        <v>122347983</v>
       </c>
       <c r="B33" t="n">
-        <v>89464</v>
+        <v>92093</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4301,38 +4286,41 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6276</v>
+        <v>5449</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>gladaberg73, Vb</t>
+          <t>gladaberg71, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>717180</v>
+        <v>717248</v>
       </c>
       <c r="R33" t="n">
-        <v>7147242</v>
+        <v>7147108</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4373,6 +4361,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4401,10 +4390,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122347983</v>
+        <v>122347973</v>
       </c>
       <c r="B34" t="n">
-        <v>92093</v>
+        <v>78383</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4417,21 +4406,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5449</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4440,14 +4429,14 @@
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>gladaberg71, Vb</t>
+          <t>gladaberg74, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>717248</v>
+        <v>717095</v>
       </c>
       <c r="R34" t="n">
-        <v>7147108</v>
+        <v>7147049</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4497,9 +4486,24 @@
           <t>Sandtallskog</t>
         </is>
       </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>äldre</t>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Stump # låg,sotad # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4517,7 +4521,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122347980</v>
+        <v>122347978</v>
       </c>
       <c r="B35" t="n">
         <v>89464</v>
@@ -4551,19 +4555,16 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>gladaberg72, Vb</t>
+          <t>gladaberg73, Vb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>717040</v>
+        <v>717180</v>
       </c>
       <c r="R35" t="n">
-        <v>7147136</v>
+        <v>7147242</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4604,7 +4605,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 48075-2023 artfynd.xlsx
+++ b/artfynd/A 48075-2023 artfynd.xlsx
@@ -1617,7 +1617,7 @@
         <v>121972026</v>
       </c>
       <c r="B10" t="n">
-        <v>92081</v>
+        <v>92093</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1730,10 +1730,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121972536</v>
+        <v>121972017</v>
       </c>
       <c r="B11" t="n">
-        <v>92059</v>
+        <v>92069</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1746,21 +1746,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1769,14 +1769,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>gladaberg24, Vb</t>
+          <t>gladaberg21, Vb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>717199</v>
+        <v>717146</v>
       </c>
       <c r="R11" t="n">
-        <v>7147036</v>
+        <v>7147163</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1846,10 +1846,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121972017</v>
+        <v>121972533</v>
       </c>
       <c r="B12" t="n">
-        <v>92057</v>
+        <v>89476</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1858,25 +1858,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4361</v>
+        <v>6276</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1885,14 +1885,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>gladaberg21, Vb</t>
+          <t>gladaberg26, Vb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>717146</v>
+        <v>717013</v>
       </c>
       <c r="R12" t="n">
-        <v>7147163</v>
+        <v>7147156</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1962,10 +1962,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121972533</v>
+        <v>121972536</v>
       </c>
       <c r="B13" t="n">
-        <v>89464</v>
+        <v>92071</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1974,25 +1974,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6276</v>
+        <v>4362</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2001,14 +2001,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>gladaberg26, Vb</t>
+          <t>gladaberg24, Vb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>717013</v>
+        <v>717199</v>
       </c>
       <c r="R13" t="n">
-        <v>7147156</v>
+        <v>7147036</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2078,10 +2078,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122009529</v>
+        <v>122009541</v>
       </c>
       <c r="B14" t="n">
-        <v>92059</v>
+        <v>89476</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2090,25 +2090,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4362</v>
+        <v>6276</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2117,14 +2117,14 @@
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>gladaberg41, Vb</t>
+          <t>gladaberg38, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>717086</v>
+        <v>717187</v>
       </c>
       <c r="R14" t="n">
-        <v>7147042</v>
+        <v>7147212</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2194,10 +2194,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122009541</v>
+        <v>122009529</v>
       </c>
       <c r="B15" t="n">
-        <v>89464</v>
+        <v>92071</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2206,25 +2206,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6276</v>
+        <v>4362</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2233,14 +2233,14 @@
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>gladaberg38, Vb</t>
+          <t>gladaberg41, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>717187</v>
+        <v>717086</v>
       </c>
       <c r="R15" t="n">
-        <v>7147212</v>
+        <v>7147042</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2313,7 +2313,7 @@
         <v>122032387</v>
       </c>
       <c r="B16" t="n">
-        <v>89464</v>
+        <v>89476</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>122032385</v>
       </c>
       <c r="B17" t="n">
-        <v>89464</v>
+        <v>89476</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>122032383</v>
       </c>
       <c r="B18" t="n">
-        <v>92081</v>
+        <v>92093</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2658,10 +2658,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122085251</v>
+        <v>122091612</v>
       </c>
       <c r="B19" t="n">
-        <v>89464</v>
+        <v>92069</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2670,38 +2670,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6276</v>
+        <v>4361</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>gladaberg48, Vb</t>
+          <t>gladaberg53, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>717011</v>
+        <v>717176</v>
       </c>
       <c r="R19" t="n">
-        <v>7147163</v>
+        <v>7147221</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2742,6 +2745,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2770,10 +2774,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122091612</v>
+        <v>122091614</v>
       </c>
       <c r="B20" t="n">
-        <v>92057</v>
+        <v>92093</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2786,21 +2790,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2809,14 +2813,14 @@
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>gladaberg53, Vb</t>
+          <t>gladaberg52, Vb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>717176</v>
+        <v>717310</v>
       </c>
       <c r="R20" t="n">
-        <v>7147221</v>
+        <v>7147007</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2889,7 +2893,7 @@
         <v>122091604</v>
       </c>
       <c r="B21" t="n">
-        <v>92081</v>
+        <v>92093</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3002,10 +3006,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122091602</v>
+        <v>122085242</v>
       </c>
       <c r="B22" t="n">
-        <v>92081</v>
+        <v>89476</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3014,38 +3018,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2059</v>
+        <v>6276</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>gladaberg57, Vb</t>
+          <t>gladaberg49, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>717274</v>
+        <v>717095</v>
       </c>
       <c r="R22" t="n">
-        <v>7147076</v>
+        <v>7147068</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3086,6 +3093,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3114,10 +3122,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122091614</v>
+        <v>122085239</v>
       </c>
       <c r="B23" t="n">
-        <v>92081</v>
+        <v>92069</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3130,21 +3138,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3153,14 +3161,14 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>gladaberg52, Vb</t>
+          <t>gladaberg50, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>717310</v>
+        <v>717309</v>
       </c>
       <c r="R23" t="n">
-        <v>7147007</v>
+        <v>7146939</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3230,10 +3238,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122085242</v>
+        <v>122091602</v>
       </c>
       <c r="B24" t="n">
-        <v>89464</v>
+        <v>92093</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3242,41 +3250,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6276</v>
+        <v>2059</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>gladaberg49, Vb</t>
+          <t>gladaberg57, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>717095</v>
+        <v>717274</v>
       </c>
       <c r="R24" t="n">
-        <v>7147068</v>
+        <v>7147076</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3317,7 +3322,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3346,10 +3350,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122085239</v>
+        <v>122085251</v>
       </c>
       <c r="B25" t="n">
-        <v>92057</v>
+        <v>89476</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3358,41 +3362,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4361</v>
+        <v>6276</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>gladaberg50, Vb</t>
+          <t>gladaberg48, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>717309</v>
+        <v>717011</v>
       </c>
       <c r="R25" t="n">
-        <v>7146939</v>
+        <v>7147163</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3433,7 +3434,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3462,10 +3462,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122106357</v>
+        <v>122106356</v>
       </c>
       <c r="B26" t="n">
-        <v>92057</v>
+        <v>89476</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3474,25 +3474,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4361</v>
+        <v>6276</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3501,14 +3501,14 @@
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>gladaberg61, Vb</t>
+          <t>gladaberg62, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>717038</v>
+        <v>717129</v>
       </c>
       <c r="R26" t="n">
-        <v>7147114</v>
+        <v>7147026</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3578,10 +3578,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122106356</v>
+        <v>122106363</v>
       </c>
       <c r="B27" t="n">
-        <v>89464</v>
+        <v>92093</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3590,25 +3590,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6276</v>
+        <v>2059</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3617,14 +3617,14 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>gladaberg62, Vb</t>
+          <t>gladaberg60, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>717129</v>
+        <v>717060</v>
       </c>
       <c r="R27" t="n">
-        <v>7147026</v>
+        <v>7147112</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3694,10 +3694,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122106363</v>
+        <v>122106357</v>
       </c>
       <c r="B28" t="n">
-        <v>92081</v>
+        <v>92069</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3710,21 +3710,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3733,14 +3733,14 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>gladaberg60, Vb</t>
+          <t>gladaberg61, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>717060</v>
+        <v>717038</v>
       </c>
       <c r="R28" t="n">
-        <v>7147112</v>
+        <v>7147114</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3813,7 +3813,7 @@
         <v>122232479</v>
       </c>
       <c r="B29" t="n">
-        <v>89464</v>
+        <v>89476</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3926,10 +3926,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122232491</v>
+        <v>122232499</v>
       </c>
       <c r="B30" t="n">
-        <v>92059</v>
+        <v>92093</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3942,21 +3942,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3965,14 +3965,14 @@
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>gladaberg67, Vb</t>
+          <t>gladaberg64, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>717247</v>
+        <v>717129</v>
       </c>
       <c r="R30" t="n">
-        <v>7147095</v>
+        <v>7147180</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4042,10 +4042,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122232499</v>
+        <v>122232491</v>
       </c>
       <c r="B31" t="n">
-        <v>92081</v>
+        <v>92071</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4058,21 +4058,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4081,14 +4081,14 @@
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>gladaberg64, Vb</t>
+          <t>gladaberg67, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>717129</v>
+        <v>717247</v>
       </c>
       <c r="R31" t="n">
-        <v>7147180</v>
+        <v>7147095</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4161,7 +4161,7 @@
         <v>122347980</v>
       </c>
       <c r="B32" t="n">
-        <v>89464</v>
+        <v>89476</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4274,10 +4274,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122347983</v>
+        <v>122347978</v>
       </c>
       <c r="B33" t="n">
-        <v>92093</v>
+        <v>89476</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4286,41 +4286,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5449</v>
+        <v>6276</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>gladaberg71, Vb</t>
+          <t>gladaberg73, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>717248</v>
+        <v>717180</v>
       </c>
       <c r="R33" t="n">
-        <v>7147108</v>
+        <v>7147242</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4361,7 +4358,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4393,7 +4389,7 @@
         <v>122347973</v>
       </c>
       <c r="B34" t="n">
-        <v>78383</v>
+        <v>78388</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4521,10 +4517,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122347978</v>
+        <v>122347983</v>
       </c>
       <c r="B35" t="n">
-        <v>89464</v>
+        <v>92105</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4533,38 +4529,41 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6276</v>
+        <v>5449</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>gladaberg73, Vb</t>
+          <t>gladaberg71, Vb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>717180</v>
+        <v>717248</v>
       </c>
       <c r="R35" t="n">
-        <v>7147242</v>
+        <v>7147108</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4605,6 +4604,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 48075-2023 artfynd.xlsx
+++ b/artfynd/A 48075-2023 artfynd.xlsx
@@ -2078,10 +2078,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122009541</v>
+        <v>122009529</v>
       </c>
       <c r="B14" t="n">
-        <v>89476</v>
+        <v>92076</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2090,25 +2090,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6276</v>
+        <v>4362</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2117,14 +2117,14 @@
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>gladaberg38, Vb</t>
+          <t>gladaberg41, Vb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>717187</v>
+        <v>717086</v>
       </c>
       <c r="R14" t="n">
-        <v>7147212</v>
+        <v>7147042</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2194,10 +2194,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122009529</v>
+        <v>122009541</v>
       </c>
       <c r="B15" t="n">
-        <v>92071</v>
+        <v>89480</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2206,25 +2206,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4362</v>
+        <v>6276</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2233,14 +2233,14 @@
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>gladaberg41, Vb</t>
+          <t>gladaberg38, Vb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>717086</v>
+        <v>717187</v>
       </c>
       <c r="R15" t="n">
-        <v>7147042</v>
+        <v>7147212</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2310,10 +2310,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122032387</v>
+        <v>122032383</v>
       </c>
       <c r="B16" t="n">
-        <v>89476</v>
+        <v>92098</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2322,25 +2322,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6276</v>
+        <v>2059</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2349,14 +2349,14 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>gladaberg42, Vb</t>
+          <t>gladaberg44, Vb</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>717138</v>
+        <v>717040</v>
       </c>
       <c r="R16" t="n">
-        <v>7147029</v>
+        <v>7147142</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2426,10 +2426,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122032385</v>
+        <v>122032387</v>
       </c>
       <c r="B17" t="n">
-        <v>89476</v>
+        <v>89480</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2465,14 +2465,14 @@
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>gladaberg43, Vb</t>
+          <t>gladaberg42, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>717203</v>
+        <v>717138</v>
       </c>
       <c r="R17" t="n">
-        <v>7147231</v>
+        <v>7147029</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2542,10 +2542,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122032383</v>
+        <v>122032385</v>
       </c>
       <c r="B18" t="n">
-        <v>92093</v>
+        <v>89480</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2554,25 +2554,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2059</v>
+        <v>6276</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2581,14 +2581,14 @@
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>gladaberg44, Vb</t>
+          <t>gladaberg43, Vb</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>717040</v>
+        <v>717203</v>
       </c>
       <c r="R18" t="n">
-        <v>7147142</v>
+        <v>7147231</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2658,10 +2658,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122091612</v>
+        <v>122091602</v>
       </c>
       <c r="B19" t="n">
-        <v>92069</v>
+        <v>92098</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2674,37 +2674,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4361</v>
+        <v>2059</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>gladaberg53, Vb</t>
+          <t>gladaberg57, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>717176</v>
+        <v>717274</v>
       </c>
       <c r="R19" t="n">
-        <v>7147221</v>
+        <v>7147076</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2745,7 +2742,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2777,7 +2773,7 @@
         <v>122091614</v>
       </c>
       <c r="B20" t="n">
-        <v>92093</v>
+        <v>92098</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2890,10 +2886,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122091604</v>
+        <v>122085251</v>
       </c>
       <c r="B21" t="n">
-        <v>92093</v>
+        <v>89480</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2902,41 +2898,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2059</v>
+        <v>6276</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>gladaberg56, Vb</t>
+          <t>gladaberg48, Vb</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>717151</v>
+        <v>717011</v>
       </c>
       <c r="R21" t="n">
-        <v>7147276</v>
+        <v>7147163</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2977,7 +2970,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3006,10 +2998,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122085242</v>
+        <v>122085239</v>
       </c>
       <c r="B22" t="n">
-        <v>89476</v>
+        <v>92074</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3018,25 +3010,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6276</v>
+        <v>4361</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3045,14 +3037,14 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>gladaberg49, Vb</t>
+          <t>gladaberg50, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>717095</v>
+        <v>717309</v>
       </c>
       <c r="R22" t="n">
-        <v>7147068</v>
+        <v>7146939</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3122,10 +3114,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122085239</v>
+        <v>122085242</v>
       </c>
       <c r="B23" t="n">
-        <v>92069</v>
+        <v>89480</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3134,25 +3126,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4361</v>
+        <v>6276</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3161,14 +3153,14 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>gladaberg50, Vb</t>
+          <t>gladaberg49, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>717309</v>
+        <v>717095</v>
       </c>
       <c r="R23" t="n">
-        <v>7146939</v>
+        <v>7147068</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3238,10 +3230,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122091602</v>
+        <v>122091612</v>
       </c>
       <c r="B24" t="n">
-        <v>92093</v>
+        <v>92074</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3254,34 +3246,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>gladaberg57, Vb</t>
+          <t>gladaberg53, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>717274</v>
+        <v>717176</v>
       </c>
       <c r="R24" t="n">
-        <v>7147076</v>
+        <v>7147221</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3322,6 +3317,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3350,10 +3346,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122085251</v>
+        <v>122091604</v>
       </c>
       <c r="B25" t="n">
-        <v>89476</v>
+        <v>92098</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3362,38 +3358,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6276</v>
+        <v>2059</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>gladaberg48, Vb</t>
+          <t>gladaberg56, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>717011</v>
+        <v>717151</v>
       </c>
       <c r="R25" t="n">
-        <v>7147163</v>
+        <v>7147276</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3434,6 +3433,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3462,10 +3462,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122106356</v>
+        <v>122106357</v>
       </c>
       <c r="B26" t="n">
-        <v>89476</v>
+        <v>92074</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3474,25 +3474,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6276</v>
+        <v>4361</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3501,14 +3501,14 @@
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>gladaberg62, Vb</t>
+          <t>gladaberg61, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>717129</v>
+        <v>717038</v>
       </c>
       <c r="R26" t="n">
-        <v>7147026</v>
+        <v>7147114</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3581,7 +3581,7 @@
         <v>122106363</v>
       </c>
       <c r="B27" t="n">
-        <v>92093</v>
+        <v>92098</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3694,10 +3694,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122106357</v>
+        <v>122106356</v>
       </c>
       <c r="B28" t="n">
-        <v>92069</v>
+        <v>89480</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3706,25 +3706,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4361</v>
+        <v>6276</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3733,14 +3733,14 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>gladaberg61, Vb</t>
+          <t>gladaberg62, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>717038</v>
+        <v>717129</v>
       </c>
       <c r="R28" t="n">
-        <v>7147114</v>
+        <v>7147026</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3813,7 +3813,7 @@
         <v>122232479</v>
       </c>
       <c r="B29" t="n">
-        <v>89476</v>
+        <v>89480</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3929,7 +3929,7 @@
         <v>122232499</v>
       </c>
       <c r="B30" t="n">
-        <v>92093</v>
+        <v>92098</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4045,7 +4045,7 @@
         <v>122232491</v>
       </c>
       <c r="B31" t="n">
-        <v>92071</v>
+        <v>92076</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4161,7 +4161,7 @@
         <v>122347980</v>
       </c>
       <c r="B32" t="n">
-        <v>89476</v>
+        <v>89480</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4274,10 +4274,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122347978</v>
+        <v>122347973</v>
       </c>
       <c r="B33" t="n">
-        <v>89476</v>
+        <v>78388</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4286,38 +4286,41 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6276</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>gladaberg73, Vb</t>
+          <t>gladaberg74, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>717180</v>
+        <v>717095</v>
       </c>
       <c r="R33" t="n">
-        <v>7147242</v>
+        <v>7147049</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4358,6 +4361,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4366,9 +4370,24 @@
           <t>Sandtallskog</t>
         </is>
       </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>äldre</t>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Stump # låg,sotad # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4386,10 +4405,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122347973</v>
+        <v>122347978</v>
       </c>
       <c r="B34" t="n">
-        <v>78388</v>
+        <v>89480</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4398,41 +4417,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>6276</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>gladaberg74, Vb</t>
+          <t>gladaberg73, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>717095</v>
+        <v>717180</v>
       </c>
       <c r="R34" t="n">
-        <v>7147049</v>
+        <v>7147242</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4473,7 +4489,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4482,24 +4497,9 @@
           <t>Sandtallskog</t>
         </is>
       </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Stump # låg,sotad # Pinus sylvestris</t>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>äldre</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4520,7 +4520,7 @@
         <v>122347983</v>
       </c>
       <c r="B35" t="n">
-        <v>92105</v>
+        <v>92110</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>

--- a/artfynd/A 48075-2023 artfynd.xlsx
+++ b/artfynd/A 48075-2023 artfynd.xlsx
@@ -2658,10 +2658,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122091602</v>
+        <v>122091614</v>
       </c>
       <c r="B19" t="n">
-        <v>92098</v>
+        <v>92103</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2676,11 +2676,6 @@
       <c r="E19" t="n">
         <v>2059</v>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Skrovlig taggsvamp</t>
-        </is>
-      </c>
       <c r="G19" t="inlineStr">
         <is>
           <t>Hydnellum scabrosum</t>
@@ -2692,16 +2687,19 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>gladaberg57, Vb</t>
+          <t>gladaberg52, Vb</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>717274</v>
+        <v>717310</v>
       </c>
       <c r="R19" t="n">
-        <v>7147076</v>
+        <v>7147007</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2742,6 +2740,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2770,10 +2769,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122091614</v>
+        <v>122085239</v>
       </c>
       <c r="B20" t="n">
-        <v>92098</v>
+        <v>92079</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2786,21 +2785,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2059</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Skrovlig taggsvamp</t>
-        </is>
+        <v>4361</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2809,14 +2803,14 @@
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>gladaberg52, Vb</t>
+          <t>gladaberg50, Vb</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>717310</v>
+        <v>717309</v>
       </c>
       <c r="R20" t="n">
-        <v>7147007</v>
+        <v>7146939</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2889,7 +2883,7 @@
         <v>122085251</v>
       </c>
       <c r="B21" t="n">
-        <v>89480</v>
+        <v>89485</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2903,11 +2897,6 @@
       </c>
       <c r="E21" t="n">
         <v>6276</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Goliatmusseron</t>
-        </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -2998,10 +2987,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122085239</v>
+        <v>122091602</v>
       </c>
       <c r="B22" t="n">
-        <v>92074</v>
+        <v>92103</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3014,37 +3003,29 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4361</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Orange taggsvamp</t>
-        </is>
+        <v>2059</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>gladaberg50, Vb</t>
+          <t>gladaberg57, Vb</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>717309</v>
+        <v>717274</v>
       </c>
       <c r="R22" t="n">
-        <v>7146939</v>
+        <v>7147076</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3085,7 +3066,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3114,10 +3094,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122085242</v>
+        <v>122091612</v>
       </c>
       <c r="B23" t="n">
-        <v>89480</v>
+        <v>92079</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3126,25 +3106,20 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6276</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Goliatmusseron</t>
-        </is>
+        <v>4361</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3153,14 +3128,14 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>gladaberg49, Vb</t>
+          <t>gladaberg53, Vb</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>717095</v>
+        <v>717176</v>
       </c>
       <c r="R23" t="n">
-        <v>7147068</v>
+        <v>7147221</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3230,10 +3205,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122091612</v>
+        <v>122091604</v>
       </c>
       <c r="B24" t="n">
-        <v>92074</v>
+        <v>92103</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3246,21 +3221,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4361</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Orange taggsvamp</t>
-        </is>
+        <v>2059</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3269,14 +3239,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>gladaberg53, Vb</t>
+          <t>gladaberg56, Vb</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>717176</v>
+        <v>717151</v>
       </c>
       <c r="R24" t="n">
-        <v>7147221</v>
+        <v>7147276</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3346,10 +3316,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122091604</v>
+        <v>122085242</v>
       </c>
       <c r="B25" t="n">
-        <v>92098</v>
+        <v>89485</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3358,25 +3328,20 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2059</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Skrovlig taggsvamp</t>
-        </is>
+        <v>6276</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3385,14 +3350,14 @@
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>gladaberg56, Vb</t>
+          <t>gladaberg49, Vb</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>717151</v>
+        <v>717095</v>
       </c>
       <c r="R25" t="n">
-        <v>7147276</v>
+        <v>7147068</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3462,10 +3427,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122106357</v>
+        <v>122106356</v>
       </c>
       <c r="B26" t="n">
-        <v>92074</v>
+        <v>89485</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3474,25 +3439,20 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4361</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Orange taggsvamp</t>
-        </is>
+        <v>6276</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3501,14 +3461,14 @@
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>gladaberg61, Vb</t>
+          <t>gladaberg62, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>717038</v>
+        <v>717129</v>
       </c>
       <c r="R26" t="n">
-        <v>7147114</v>
+        <v>7147026</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3581,7 +3541,7 @@
         <v>122106363</v>
       </c>
       <c r="B27" t="n">
-        <v>92098</v>
+        <v>92103</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3595,11 +3555,6 @@
       </c>
       <c r="E27" t="n">
         <v>2059</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Skrovlig taggsvamp</t>
-        </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -3694,10 +3649,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122106356</v>
+        <v>122106357</v>
       </c>
       <c r="B28" t="n">
-        <v>89480</v>
+        <v>92079</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3706,25 +3661,20 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6276</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Goliatmusseron</t>
-        </is>
+        <v>4361</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3733,14 +3683,14 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>gladaberg62, Vb</t>
+          <t>gladaberg61, Vb</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>717129</v>
+        <v>717038</v>
       </c>
       <c r="R28" t="n">
-        <v>7147026</v>
+        <v>7147114</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3810,10 +3760,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122232479</v>
+        <v>122232491</v>
       </c>
       <c r="B29" t="n">
-        <v>89480</v>
+        <v>92081</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3822,25 +3772,20 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6276</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Goliatmusseron</t>
-        </is>
+        <v>4362</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3849,14 +3794,14 @@
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>gladaberg70, Vb</t>
+          <t>gladaberg67, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>717126</v>
+        <v>717247</v>
       </c>
       <c r="R29" t="n">
-        <v>7147085</v>
+        <v>7147095</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3926,10 +3871,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122232499</v>
+        <v>122232479</v>
       </c>
       <c r="B30" t="n">
-        <v>92098</v>
+        <v>89485</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3938,25 +3883,20 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2059</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Skrovlig taggsvamp</t>
-        </is>
+        <v>6276</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3965,14 +3905,14 @@
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>gladaberg64, Vb</t>
+          <t>gladaberg70, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>717129</v>
+        <v>717126</v>
       </c>
       <c r="R30" t="n">
-        <v>7147180</v>
+        <v>7147085</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4042,10 +3982,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122232491</v>
+        <v>122232499</v>
       </c>
       <c r="B31" t="n">
-        <v>92076</v>
+        <v>92103</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4058,21 +3998,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4362</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Blå taggsvamp</t>
-        </is>
+        <v>2059</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4081,14 +4016,14 @@
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>gladaberg67, Vb</t>
+          <t>gladaberg64, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>717247</v>
+        <v>717129</v>
       </c>
       <c r="R31" t="n">
-        <v>7147095</v>
+        <v>7147180</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4161,7 +4096,7 @@
         <v>122347980</v>
       </c>
       <c r="B32" t="n">
-        <v>89480</v>
+        <v>89485</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4175,11 +4110,6 @@
       </c>
       <c r="E32" t="n">
         <v>6276</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Goliatmusseron</t>
-        </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -4277,7 +4207,7 @@
         <v>122347973</v>
       </c>
       <c r="B33" t="n">
-        <v>78388</v>
+        <v>78389</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4291,11 +4221,6 @@
       </c>
       <c r="E33" t="n">
         <v>228912</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -4370,11 +4295,6 @@
           <t>Sandtallskog</t>
         </is>
       </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
       <c r="AK33" t="inlineStr">
         <is>
           <t>Pinus sylvestris</t>
@@ -4405,10 +4325,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122347978</v>
+        <v>122347983</v>
       </c>
       <c r="B34" t="n">
-        <v>89480</v>
+        <v>92115</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4417,38 +4337,36 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6276</v>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Goliatmusseron</t>
-        </is>
+        <v>5449</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>gladaberg73, Vb</t>
+          <t>gladaberg71, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>717180</v>
+        <v>717248</v>
       </c>
       <c r="R34" t="n">
-        <v>7147242</v>
+        <v>7147108</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4489,6 +4407,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4517,10 +4436,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122347983</v>
+        <v>122347978</v>
       </c>
       <c r="B35" t="n">
-        <v>92110</v>
+        <v>89485</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4529,41 +4448,33 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5449</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Svart taggsvamp</t>
-        </is>
+        <v>6276</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>gladaberg71, Vb</t>
+          <t>gladaberg73, Vb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>717248</v>
+        <v>717180</v>
       </c>
       <c r="R35" t="n">
-        <v>7147108</v>
+        <v>7147242</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4604,7 +4515,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 48075-2023 artfynd.xlsx
+++ b/artfynd/A 48075-2023 artfynd.xlsx
@@ -3427,10 +3427,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122106356</v>
+        <v>122106363</v>
       </c>
       <c r="B26" t="n">
-        <v>89485</v>
+        <v>92116</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3439,20 +3439,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6276</v>
+        <v>2059</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Skrovlig taggsvamp</t>
+        </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3461,14 +3466,14 @@
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>gladaberg62, Vb</t>
+          <t>gladaberg60, Vb</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>717129</v>
+        <v>717060</v>
       </c>
       <c r="R26" t="n">
-        <v>7147026</v>
+        <v>7147112</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3538,10 +3543,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122106363</v>
+        <v>122106356</v>
       </c>
       <c r="B27" t="n">
-        <v>92103</v>
+        <v>89498</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3550,20 +3555,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2059</v>
+        <v>6276</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Goliatmusseron</t>
+        </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3572,14 +3582,14 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>gladaberg60, Vb</t>
+          <t>gladaberg62, Vb</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>717060</v>
+        <v>717129</v>
       </c>
       <c r="R27" t="n">
-        <v>7147112</v>
+        <v>7147026</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3652,7 +3662,7 @@
         <v>122106357</v>
       </c>
       <c r="B28" t="n">
-        <v>92079</v>
+        <v>92092</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3666,6 +3676,11 @@
       </c>
       <c r="E28" t="n">
         <v>4361</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -3760,10 +3775,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122232491</v>
+        <v>122232479</v>
       </c>
       <c r="B29" t="n">
-        <v>92081</v>
+        <v>89498</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3772,20 +3787,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4362</v>
+        <v>6276</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Goliatmusseron</t>
+        </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3794,14 +3814,14 @@
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>gladaberg67, Vb</t>
+          <t>gladaberg70, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>717247</v>
+        <v>717126</v>
       </c>
       <c r="R29" t="n">
-        <v>7147095</v>
+        <v>7147085</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3871,10 +3891,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122232479</v>
+        <v>122232499</v>
       </c>
       <c r="B30" t="n">
-        <v>89485</v>
+        <v>92116</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3883,20 +3903,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6276</v>
+        <v>2059</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Skrovlig taggsvamp</t>
+        </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3905,14 +3930,14 @@
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>gladaberg70, Vb</t>
+          <t>gladaberg64, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>717126</v>
+        <v>717129</v>
       </c>
       <c r="R30" t="n">
-        <v>7147085</v>
+        <v>7147180</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3982,10 +4007,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122232499</v>
+        <v>122232491</v>
       </c>
       <c r="B31" t="n">
-        <v>92103</v>
+        <v>92094</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3998,16 +4023,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2059</v>
+        <v>4362</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4016,14 +4046,14 @@
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>gladaberg64, Vb</t>
+          <t>gladaberg67, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>717129</v>
+        <v>717247</v>
       </c>
       <c r="R31" t="n">
-        <v>7147180</v>
+        <v>7147095</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4093,10 +4123,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122347980</v>
+        <v>122347983</v>
       </c>
       <c r="B32" t="n">
-        <v>89485</v>
+        <v>92128</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4105,20 +4135,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6276</v>
+        <v>5449</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4127,14 +4162,14 @@
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>gladaberg72, Vb</t>
+          <t>gladaberg71, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>717040</v>
+        <v>717248</v>
       </c>
       <c r="R32" t="n">
-        <v>7147136</v>
+        <v>7147108</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4207,7 +4242,7 @@
         <v>122347973</v>
       </c>
       <c r="B33" t="n">
-        <v>78389</v>
+        <v>78393</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4221,6 +4256,11 @@
       </c>
       <c r="E33" t="n">
         <v>228912</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -4295,6 +4335,11 @@
           <t>Sandtallskog</t>
         </is>
       </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
       <c r="AK33" t="inlineStr">
         <is>
           <t>Pinus sylvestris</t>
@@ -4325,10 +4370,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122347983</v>
+        <v>122347978</v>
       </c>
       <c r="B34" t="n">
-        <v>92115</v>
+        <v>89498</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4337,36 +4382,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5449</v>
+        <v>6276</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Goliatmusseron</t>
+        </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>gladaberg71, Vb</t>
+          <t>gladaberg73, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>717248</v>
+        <v>717180</v>
       </c>
       <c r="R34" t="n">
-        <v>7147108</v>
+        <v>7147242</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4407,7 +4454,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4436,10 +4482,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122347978</v>
+        <v>122347980</v>
       </c>
       <c r="B35" t="n">
-        <v>89485</v>
+        <v>89498</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4454,6 +4500,11 @@
       <c r="E35" t="n">
         <v>6276</v>
       </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Goliatmusseron</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr">
         <is>
           <t>Tricholoma matsutake</t>
@@ -4465,16 +4516,19 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>gladaberg73, Vb</t>
+          <t>gladaberg72, Vb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>717180</v>
+        <v>717040</v>
       </c>
       <c r="R35" t="n">
-        <v>7147242</v>
+        <v>7147136</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4515,6 +4569,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 48075-2023 artfynd.xlsx
+++ b/artfynd/A 48075-2023 artfynd.xlsx
@@ -3775,10 +3775,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122232479</v>
+        <v>122232491</v>
       </c>
       <c r="B29" t="n">
-        <v>89498</v>
+        <v>92107</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3787,25 +3787,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6276</v>
+        <v>4362</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3814,14 +3814,14 @@
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>gladaberg70, Vb</t>
+          <t>gladaberg67, Vb</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>717126</v>
+        <v>717247</v>
       </c>
       <c r="R29" t="n">
-        <v>7147085</v>
+        <v>7147095</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3891,10 +3891,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122232499</v>
+        <v>122232479</v>
       </c>
       <c r="B30" t="n">
-        <v>92116</v>
+        <v>89510</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3903,25 +3903,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2059</v>
+        <v>6276</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3930,14 +3930,14 @@
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>gladaberg64, Vb</t>
+          <t>gladaberg70, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>717129</v>
+        <v>717126</v>
       </c>
       <c r="R30" t="n">
-        <v>7147180</v>
+        <v>7147085</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4007,10 +4007,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122232491</v>
+        <v>122232499</v>
       </c>
       <c r="B31" t="n">
-        <v>92094</v>
+        <v>92129</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4023,21 +4023,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4046,14 +4046,14 @@
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>gladaberg67, Vb</t>
+          <t>gladaberg64, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>717247</v>
+        <v>717129</v>
       </c>
       <c r="R31" t="n">
-        <v>7147095</v>
+        <v>7147180</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4126,7 +4126,7 @@
         <v>122347983</v>
       </c>
       <c r="B32" t="n">
-        <v>92128</v>
+        <v>92141</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4239,10 +4239,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122347973</v>
+        <v>122347978</v>
       </c>
       <c r="B33" t="n">
-        <v>78393</v>
+        <v>89510</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4251,41 +4251,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>6276</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>gladaberg74, Vb</t>
+          <t>gladaberg73, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>717095</v>
+        <v>717180</v>
       </c>
       <c r="R33" t="n">
-        <v>7147049</v>
+        <v>7147242</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4326,7 +4323,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4335,24 +4331,9 @@
           <t>Sandtallskog</t>
         </is>
       </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Stump # låg,sotad # Pinus sylvestris</t>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>äldre</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4370,10 +4351,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122347978</v>
+        <v>122347973</v>
       </c>
       <c r="B34" t="n">
-        <v>89498</v>
+        <v>78393</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4382,38 +4363,41 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6276</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>gladaberg73, Vb</t>
+          <t>gladaberg74, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>717180</v>
+        <v>717095</v>
       </c>
       <c r="R34" t="n">
-        <v>7147242</v>
+        <v>7147049</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4454,6 +4438,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4462,9 +4447,24 @@
           <t>Sandtallskog</t>
         </is>
       </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>äldre</t>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Stump # låg,sotad # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4485,7 +4485,7 @@
         <v>122347980</v>
       </c>
       <c r="B35" t="n">
-        <v>89498</v>
+        <v>89510</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>

--- a/artfynd/A 48075-2023 artfynd.xlsx
+++ b/artfynd/A 48075-2023 artfynd.xlsx
@@ -4351,10 +4351,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122347973</v>
+        <v>122347980</v>
       </c>
       <c r="B34" t="n">
-        <v>78393</v>
+        <v>89510</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4363,25 +4363,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>6276</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4390,14 +4390,14 @@
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>gladaberg74, Vb</t>
+          <t>gladaberg72, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>717095</v>
+        <v>717040</v>
       </c>
       <c r="R34" t="n">
-        <v>7147049</v>
+        <v>7147136</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4447,24 +4447,9 @@
           <t>Sandtallskog</t>
         </is>
       </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Stump # låg,sotad # Pinus sylvestris</t>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>äldre</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4482,10 +4467,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122347980</v>
+        <v>122347973</v>
       </c>
       <c r="B35" t="n">
-        <v>89510</v>
+        <v>78393</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4494,25 +4479,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6276</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4521,14 +4506,14 @@
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>gladaberg72, Vb</t>
+          <t>gladaberg74, Vb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>717040</v>
+        <v>717095</v>
       </c>
       <c r="R35" t="n">
-        <v>7147136</v>
+        <v>7147049</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4578,9 +4563,24 @@
           <t>Sandtallskog</t>
         </is>
       </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>äldre</t>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Stump # låg,sotad # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>

--- a/artfynd/A 48075-2023 artfynd.xlsx
+++ b/artfynd/A 48075-2023 artfynd.xlsx
@@ -3891,10 +3891,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122232479</v>
+        <v>122232499</v>
       </c>
       <c r="B30" t="n">
-        <v>89510</v>
+        <v>92129</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3903,25 +3903,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6276</v>
+        <v>2059</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3930,14 +3930,14 @@
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>gladaberg70, Vb</t>
+          <t>gladaberg64, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>717126</v>
+        <v>717129</v>
       </c>
       <c r="R30" t="n">
-        <v>7147085</v>
+        <v>7147180</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4007,10 +4007,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122232499</v>
+        <v>122232479</v>
       </c>
       <c r="B31" t="n">
-        <v>92129</v>
+        <v>89510</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4019,25 +4019,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2059</v>
+        <v>6276</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4046,14 +4046,14 @@
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>gladaberg64, Vb</t>
+          <t>gladaberg70, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>717129</v>
+        <v>717126</v>
       </c>
       <c r="R31" t="n">
-        <v>7147180</v>
+        <v>7147085</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4123,10 +4123,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122347983</v>
+        <v>122347978</v>
       </c>
       <c r="B32" t="n">
-        <v>92141</v>
+        <v>89510</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4135,41 +4135,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5449</v>
+        <v>6276</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>gladaberg71, Vb</t>
+          <t>gladaberg73, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>717248</v>
+        <v>717180</v>
       </c>
       <c r="R32" t="n">
-        <v>7147108</v>
+        <v>7147242</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4210,7 +4207,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4239,7 +4235,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122347978</v>
+        <v>122347980</v>
       </c>
       <c r="B33" t="n">
         <v>89510</v>
@@ -4273,16 +4269,19 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>gladaberg73, Vb</t>
+          <t>gladaberg72, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>717180</v>
+        <v>717040</v>
       </c>
       <c r="R33" t="n">
-        <v>7147242</v>
+        <v>7147136</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4323,6 +4322,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4351,10 +4351,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122347980</v>
+        <v>122347973</v>
       </c>
       <c r="B34" t="n">
-        <v>89510</v>
+        <v>78393</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4363,25 +4363,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6276</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4390,14 +4390,14 @@
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>gladaberg72, Vb</t>
+          <t>gladaberg74, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>717040</v>
+        <v>717095</v>
       </c>
       <c r="R34" t="n">
-        <v>7147136</v>
+        <v>7147049</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4447,9 +4447,24 @@
           <t>Sandtallskog</t>
         </is>
       </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>äldre</t>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Stump # låg,sotad # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4467,10 +4482,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122347973</v>
+        <v>122347983</v>
       </c>
       <c r="B35" t="n">
-        <v>78393</v>
+        <v>92141</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4483,21 +4498,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>5449</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4506,14 +4521,14 @@
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>gladaberg74, Vb</t>
+          <t>gladaberg71, Vb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>717095</v>
+        <v>717248</v>
       </c>
       <c r="R35" t="n">
-        <v>7147049</v>
+        <v>7147108</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4563,24 +4578,9 @@
           <t>Sandtallskog</t>
         </is>
       </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Stump # låg,sotad # Pinus sylvestris</t>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>äldre</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>

--- a/artfynd/A 48075-2023 artfynd.xlsx
+++ b/artfynd/A 48075-2023 artfynd.xlsx
@@ -3778,7 +3778,7 @@
         <v>122232491</v>
       </c>
       <c r="B29" t="n">
-        <v>92107</v>
+        <v>92108</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3894,7 +3894,7 @@
         <v>122232499</v>
       </c>
       <c r="B30" t="n">
-        <v>92129</v>
+        <v>92130</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122347978</v>
+        <v>122347980</v>
       </c>
       <c r="B32" t="n">
         <v>89510</v>
@@ -4157,16 +4157,19 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>gladaberg73, Vb</t>
+          <t>gladaberg72, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>717180</v>
+        <v>717040</v>
       </c>
       <c r="R32" t="n">
-        <v>7147242</v>
+        <v>7147136</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4207,6 +4210,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4235,10 +4239,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122347980</v>
+        <v>122347983</v>
       </c>
       <c r="B33" t="n">
-        <v>89510</v>
+        <v>92142</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4247,25 +4251,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6276</v>
+        <v>5449</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4274,14 +4278,14 @@
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>gladaberg72, Vb</t>
+          <t>gladaberg71, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>717040</v>
+        <v>717248</v>
       </c>
       <c r="R33" t="n">
-        <v>7147136</v>
+        <v>7147108</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4482,10 +4486,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122347983</v>
+        <v>122347978</v>
       </c>
       <c r="B35" t="n">
-        <v>92141</v>
+        <v>89510</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4494,41 +4498,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5449</v>
+        <v>6276</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>gladaberg71, Vb</t>
+          <t>gladaberg73, Vb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>717248</v>
+        <v>717180</v>
       </c>
       <c r="R35" t="n">
-        <v>7147108</v>
+        <v>7147242</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4569,7 +4570,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 48075-2023 artfynd.xlsx
+++ b/artfynd/A 48075-2023 artfynd.xlsx
@@ -3891,10 +3891,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122232499</v>
+        <v>122232479</v>
       </c>
       <c r="B30" t="n">
-        <v>92130</v>
+        <v>89510</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3903,25 +3903,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2059</v>
+        <v>6276</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3930,14 +3930,14 @@
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>gladaberg64, Vb</t>
+          <t>gladaberg70, Vb</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>717129</v>
+        <v>717126</v>
       </c>
       <c r="R30" t="n">
-        <v>7147180</v>
+        <v>7147085</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4007,10 +4007,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122232479</v>
+        <v>122232499</v>
       </c>
       <c r="B31" t="n">
-        <v>89510</v>
+        <v>92130</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4019,25 +4019,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6276</v>
+        <v>2059</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4046,14 +4046,14 @@
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>gladaberg70, Vb</t>
+          <t>gladaberg64, Vb</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>717126</v>
+        <v>717129</v>
       </c>
       <c r="R31" t="n">
-        <v>7147085</v>
+        <v>7147180</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4123,7 +4123,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122347980</v>
+        <v>122347978</v>
       </c>
       <c r="B32" t="n">
         <v>89510</v>
@@ -4157,19 +4157,16 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>gladaberg72, Vb</t>
+          <t>gladaberg73, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>717040</v>
+        <v>717180</v>
       </c>
       <c r="R32" t="n">
-        <v>7147136</v>
+        <v>7147242</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4210,7 +4207,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4239,10 +4235,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122347983</v>
+        <v>122347973</v>
       </c>
       <c r="B33" t="n">
-        <v>92142</v>
+        <v>78393</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4255,21 +4251,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5449</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4278,14 +4274,14 @@
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>gladaberg71, Vb</t>
+          <t>gladaberg74, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>717248</v>
+        <v>717095</v>
       </c>
       <c r="R33" t="n">
-        <v>7147108</v>
+        <v>7147049</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4335,9 +4331,24 @@
           <t>Sandtallskog</t>
         </is>
       </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>äldre</t>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Stump # låg,sotad # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4355,10 +4366,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122347973</v>
+        <v>122347983</v>
       </c>
       <c r="B34" t="n">
-        <v>78393</v>
+        <v>92142</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4371,21 +4382,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>5449</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4394,14 +4405,14 @@
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>gladaberg74, Vb</t>
+          <t>gladaberg71, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>717095</v>
+        <v>717248</v>
       </c>
       <c r="R34" t="n">
-        <v>7147049</v>
+        <v>7147108</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4451,24 +4462,9 @@
           <t>Sandtallskog</t>
         </is>
       </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Stump # låg,sotad # Pinus sylvestris</t>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>äldre</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4486,7 +4482,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122347978</v>
+        <v>122347980</v>
       </c>
       <c r="B35" t="n">
         <v>89510</v>
@@ -4520,16 +4516,19 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>gladaberg73, Vb</t>
+          <t>gladaberg72, Vb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>717180</v>
+        <v>717040</v>
       </c>
       <c r="R35" t="n">
-        <v>7147242</v>
+        <v>7147136</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4570,6 +4569,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 48075-2023 artfynd.xlsx
+++ b/artfynd/A 48075-2023 artfynd.xlsx
@@ -4123,10 +4123,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122347978</v>
+        <v>122347973</v>
       </c>
       <c r="B32" t="n">
-        <v>89510</v>
+        <v>78394</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4135,38 +4135,41 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6276</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>gladaberg73, Vb</t>
+          <t>gladaberg74, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>717180</v>
+        <v>717095</v>
       </c>
       <c r="R32" t="n">
-        <v>7147242</v>
+        <v>7147049</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4207,6 +4210,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4215,9 +4219,24 @@
           <t>Sandtallskog</t>
         </is>
       </c>
-      <c r="AI32" t="inlineStr">
-        <is>
-          <t>äldre</t>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Stump # låg,sotad # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4235,10 +4254,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122347973</v>
+        <v>122347978</v>
       </c>
       <c r="B33" t="n">
-        <v>78393</v>
+        <v>89511</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4247,41 +4266,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>6276</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>gladaberg74, Vb</t>
+          <t>gladaberg73, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>717095</v>
+        <v>717180</v>
       </c>
       <c r="R33" t="n">
-        <v>7147049</v>
+        <v>7147242</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4322,7 +4338,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4331,24 +4346,9 @@
           <t>Sandtallskog</t>
         </is>
       </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Stump # låg,sotad # Pinus sylvestris</t>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>äldre</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4366,10 +4366,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122347983</v>
+        <v>122347980</v>
       </c>
       <c r="B34" t="n">
-        <v>92142</v>
+        <v>89511</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4378,25 +4378,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5449</v>
+        <v>6276</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4405,14 +4405,14 @@
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>gladaberg71, Vb</t>
+          <t>gladaberg72, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>717248</v>
+        <v>717040</v>
       </c>
       <c r="R34" t="n">
-        <v>7147108</v>
+        <v>7147136</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4482,10 +4482,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122347980</v>
+        <v>122347983</v>
       </c>
       <c r="B35" t="n">
-        <v>89510</v>
+        <v>92143</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4494,25 +4494,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6276</v>
+        <v>5449</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4521,14 +4521,14 @@
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>gladaberg72, Vb</t>
+          <t>gladaberg71, Vb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>717040</v>
+        <v>717248</v>
       </c>
       <c r="R35" t="n">
-        <v>7147136</v>
+        <v>7147108</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>

--- a/artfynd/A 48075-2023 artfynd.xlsx
+++ b/artfynd/A 48075-2023 artfynd.xlsx
@@ -4123,10 +4123,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122347973</v>
+        <v>122347978</v>
       </c>
       <c r="B32" t="n">
-        <v>78394</v>
+        <v>89514</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4135,41 +4135,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>6276</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>gladaberg74, Vb</t>
+          <t>gladaberg73, Vb</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>717095</v>
+        <v>717180</v>
       </c>
       <c r="R32" t="n">
-        <v>7147049</v>
+        <v>7147242</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4210,7 +4207,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4219,24 +4215,9 @@
           <t>Sandtallskog</t>
         </is>
       </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Stump # låg,sotad # Pinus sylvestris</t>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>äldre</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4254,10 +4235,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122347978</v>
+        <v>122347983</v>
       </c>
       <c r="B33" t="n">
-        <v>89511</v>
+        <v>92146</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4266,38 +4247,41 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6276</v>
+        <v>5449</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>gladaberg73, Vb</t>
+          <t>gladaberg71, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>717180</v>
+        <v>717248</v>
       </c>
       <c r="R33" t="n">
-        <v>7147242</v>
+        <v>7147108</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4338,6 +4322,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4369,7 +4354,7 @@
         <v>122347980</v>
       </c>
       <c r="B34" t="n">
-        <v>89511</v>
+        <v>89514</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4482,10 +4467,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122347983</v>
+        <v>122347973</v>
       </c>
       <c r="B35" t="n">
-        <v>92143</v>
+        <v>78397</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4498,21 +4483,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5449</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4521,14 +4506,14 @@
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>gladaberg71, Vb</t>
+          <t>gladaberg74, Vb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>717248</v>
+        <v>717095</v>
       </c>
       <c r="R35" t="n">
-        <v>7147108</v>
+        <v>7147049</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4578,9 +4563,24 @@
           <t>Sandtallskog</t>
         </is>
       </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>äldre</t>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Stump # låg,sotad # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>

--- a/artfynd/A 48075-2023 artfynd.xlsx
+++ b/artfynd/A 48075-2023 artfynd.xlsx
@@ -4235,10 +4235,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122347983</v>
+        <v>122347980</v>
       </c>
       <c r="B33" t="n">
-        <v>92146</v>
+        <v>89514</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4247,25 +4247,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5449</v>
+        <v>6276</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4274,14 +4274,14 @@
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>gladaberg71, Vb</t>
+          <t>gladaberg72, Vb</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>717248</v>
+        <v>717040</v>
       </c>
       <c r="R33" t="n">
-        <v>7147108</v>
+        <v>7147136</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4351,10 +4351,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122347980</v>
+        <v>122347973</v>
       </c>
       <c r="B34" t="n">
-        <v>89514</v>
+        <v>78397</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4363,25 +4363,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6276</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4390,14 +4390,14 @@
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>gladaberg72, Vb</t>
+          <t>gladaberg74, Vb</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>717040</v>
+        <v>717095</v>
       </c>
       <c r="R34" t="n">
-        <v>7147136</v>
+        <v>7147049</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4447,9 +4447,24 @@
           <t>Sandtallskog</t>
         </is>
       </c>
-      <c r="AI34" t="inlineStr">
-        <is>
-          <t>äldre</t>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Stubbe</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Stump # låg,sotad # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4467,10 +4482,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122347973</v>
+        <v>122347983</v>
       </c>
       <c r="B35" t="n">
-        <v>78397</v>
+        <v>92146</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4483,21 +4498,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>5449</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4506,14 +4521,14 @@
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>gladaberg74, Vb</t>
+          <t>gladaberg71, Vb</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>717095</v>
+        <v>717248</v>
       </c>
       <c r="R35" t="n">
-        <v>7147049</v>
+        <v>7147108</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4563,24 +4578,9 @@
           <t>Sandtallskog</t>
         </is>
       </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Stubbe</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Stump # låg,sotad # Pinus sylvestris</t>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>äldre</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
